--- a/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4583,6 +4583,22 @@
       </c>
       <c r="D260" t="n">
         <v>8.1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C261" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="D261" t="n">
+        <v>5.4</v>
       </c>
     </row>
   </sheetData>
@@ -4596,7 +4612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8767,6 +8783,22 @@
         <v>34</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C261" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D261" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25.1</v>
+        <v>19.3</v>
       </c>
       <c r="C56" t="n">
         <v>33.3</v>
@@ -3986,9 +3986,7 @@
       <c r="B223" t="n">
         <v>17.3</v>
       </c>
-      <c r="C223" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
         <v>5.3</v>
       </c>
@@ -4005,9 +4003,7 @@
       <c r="C224" t="n">
         <v>34.5</v>
       </c>
-      <c r="D224" t="n">
-        <v>-1.1</v>
-      </c>
+      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4476,112 +4472,96 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-4.1</v>
+        <v>-15.2</v>
       </c>
       <c r="C254" t="n">
-        <v>16.9</v>
+        <v>2.3</v>
       </c>
       <c r="D254" t="n">
-        <v>-17.1</v>
+        <v>-27.4</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>-15.2</v>
+        <v>-5</v>
       </c>
       <c r="C255" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
       <c r="D255" t="n">
-        <v>-27.4</v>
+        <v>-25.4</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>-5</v>
+        <v>3.7</v>
       </c>
       <c r="C256" t="n">
-        <v>12.9</v>
+        <v>22.2</v>
       </c>
       <c r="D256" t="n">
-        <v>-25.4</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
       <c r="C257" t="n">
-        <v>22.2</v>
+        <v>30.9</v>
       </c>
       <c r="D257" t="n">
-        <v>-11.3</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="C258" t="n">
-        <v>30.9</v>
+        <v>28.3</v>
       </c>
       <c r="D258" t="n">
-        <v>-2.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="C259" t="n">
-        <v>28.3</v>
+        <v>34</v>
       </c>
       <c r="D259" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="C260" t="n">
-        <v>34</v>
-      </c>
-      <c r="D260" t="n">
         <v>8.1</v>
       </c>
     </row>
@@ -4596,7 +4576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5498,7 +5478,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25.1</v>
+        <v>19.3</v>
       </c>
       <c r="C56" t="n">
         <v>10.2</v>
@@ -8171,9 +8151,7 @@
       <c r="C223" t="n">
         <v>5.3</v>
       </c>
-      <c r="D223" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8184,9 +8162,7 @@
       <c r="B224" t="n">
         <v>17.9</v>
       </c>
-      <c r="C224" t="n">
-        <v>-1.1</v>
-      </c>
+      <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
         <v>34.5</v>
       </c>
@@ -8658,112 +8634,96 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-4.1</v>
+        <v>-15.2</v>
       </c>
       <c r="C254" t="n">
-        <v>-17.1</v>
+        <v>-27.4</v>
       </c>
       <c r="D254" t="n">
-        <v>16.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>-15.2</v>
+        <v>-5</v>
       </c>
       <c r="C255" t="n">
-        <v>-27.4</v>
+        <v>-25.4</v>
       </c>
       <c r="D255" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>-5</v>
+        <v>3.7</v>
       </c>
       <c r="C256" t="n">
-        <v>-25.4</v>
+        <v>-11.3</v>
       </c>
       <c r="D256" t="n">
-        <v>12.9</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
       <c r="C257" t="n">
-        <v>-11.3</v>
+        <v>-2.3</v>
       </c>
       <c r="D257" t="n">
-        <v>22.2</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="C258" t="n">
-        <v>-2.3</v>
+        <v>0.2</v>
       </c>
       <c r="D258" t="n">
-        <v>30.9</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="C259" t="n">
-        <v>0.2</v>
+        <v>8.1</v>
       </c>
       <c r="D259" t="n">
-        <v>28.3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="C260" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="D260" t="n">
         <v>34</v>
       </c>
     </row>

--- a/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4579,6 +4579,22 @@
       </c>
       <c r="D260" t="n">
         <v>5.4</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="C261" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D261" t="n">
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -4592,7 +4608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8759,6 +8775,22 @@
         <v>31.3</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D261" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
